--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:14:26+00:00</t>
+    <t>2026-10-14T13:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -715,7 +715,7 @@
     <t>Gesundheitsdiensteanbieter-OID (GDA-OID)</t>
   </si>
   <si>
-    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index, maintained by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
+    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index. The OID is assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.id</t>
@@ -739,7 +739,7 @@
     <t>Practitioner.identifier:GDA-OID.system</t>
   </si>
   <si>
-    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via an URI (OID)</t>
+    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via a URI (OID)</t>
   </si>
   <si>
     <t>urn:ietf:rfc:3986</t>
@@ -933,7 +933,7 @@
     <t>Verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK)</t>
   </si>
   <si>
-    <t>The encrypted sector-specific personal identifier (Verschlüsseltes bereichsspezifisches Personenkennzeichen, vbPK) of the practitioner, used in Austrian e-Government processes and assigned by the Federal Ministry of the Interior (Bundesministerium für Inneres).</t>
+    <t>The encrypted sector-specific personal identifier (Verschlüsseltes bereichsspezifisches Personenkennzeichen, vbPK) of the practitioner, used in Austrian e-Government processes. The OID of the system identifies the sector (e.g. GH for Gesundheit, SV for Sozialversicherung, AS for Amtliche Statistik) according to the E-Government-Bereichsabgrenzungsverordnung (E-Gov-BerAbgrV).</t>
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.id</t>
@@ -951,10 +951,10 @@
     <t>Practitioner.identifier:vbPK.system</t>
   </si>
   <si>
-    <t>OID for the Verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK) in Austria</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.40.0.34.4.22</t>
+    <t>OID for the specific verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK) in Austria</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/core/r4/ValueSet/at-core-vbpk</t>
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.value</t>
@@ -964,27 +964,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.reference</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.type</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.display</t>
-  </si>
-  <si>
-    <t>Bundesministerium für Inneres</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -1167,10 +1146,10 @@
 </t>
   </si>
   <si>
-    <t>Additional administrative gender (Geschlecht, Ergänzung zu 'other')</t>
-  </si>
-  <si>
-    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other'.</t>
+    <t>Additional administrative gender (Geschlecht)</t>
+  </si>
+  <si>
+    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other' (Ergänzung zu 'other').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -1675,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.5625" customWidth="true" bestFit="true"/>
@@ -7331,7 +7310,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7934,7 +7913,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -7952,13 +7931,11 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8348,7 +8325,7 @@
         <v>308</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8368,23 +8345,29 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>309</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>158</v>
+        <v>310</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8428,7 +8411,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8440,31 +8423,31 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>161</v>
+        <v>315</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>243</v>
+        <v>317</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8480,21 +8463,23 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>318</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8530,19 +8515,19 @@
         <v>21</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>166</v>
+        <v>317</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8554,16 +8539,16 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8571,10 +8556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8585,7 +8570,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8597,18 +8582,20 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>157</v>
+        <v>327</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>246</v>
+        <v>328</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>247</v>
+        <v>329</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8656,28 +8643,28 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>131</v>
+        <v>333</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8685,10 +8672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>252</v>
+        <v>335</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8699,7 +8686,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8711,18 +8698,20 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>336</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8746,13 +8735,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>256</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8770,28 +8759,28 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>258</v>
+        <v>335</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>341</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>131</v>
+        <v>343</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8799,10 +8788,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>260</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8825,18 +8814,18 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8860,13 +8849,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8884,7 +8873,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>264</v>
+        <v>345</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8899,13 +8888,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>265</v>
+        <v>352</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8913,10 +8902,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>267</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8936,27 +8925,25 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>268</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8998,7 +8985,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>272</v>
+        <v>160</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9010,13 +8997,13 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
@@ -9027,10 +9014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9041,7 +9028,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9050,29 +9037,23 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>316</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9104,53 +9085,53 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>315</v>
+        <v>166</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9159,7 +9140,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9168,23 +9149,19 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9232,7 +9209,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>324</v>
+        <v>166</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9241,19 +9218,19 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9261,10 +9238,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9275,7 +9252,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9284,23 +9261,19 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>334</v>
+        <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9348,28 +9321,28 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9377,10 +9350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9391,7 +9364,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -9403,19 +9376,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9464,28 +9435,28 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>348</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9493,10 +9464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9507,7 +9478,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9516,20 +9487,20 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>378</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9554,13 +9525,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9578,13 +9549,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -9593,13 +9564,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9607,10 +9578,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9621,7 +9592,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -9633,13 +9604,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>157</v>
+        <v>385</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9690,28 +9661,28 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>160</v>
+        <v>384</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9719,10 +9690,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9733,7 +9704,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -9745,13 +9716,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>366</v>
+        <v>159</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9790,35 +9761,37 @@
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
@@ -9829,23 +9802,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -9857,15 +9828,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9923,7 +9896,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>139</v>
@@ -9932,7 +9905,7 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
@@ -9943,42 +9916,46 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10026,25 +10003,25 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -10055,10 +10032,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10069,7 +10046,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10078,20 +10055,20 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>377</v>
+        <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10140,13 +10117,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10155,13 +10132,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10169,10 +10146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10180,10 +10157,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10195,18 +10172,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>385</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>388</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10230,13 +10205,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>21</v>
+        <v>406</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10254,13 +10229,13 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
@@ -10275,7 +10250,7 @@
         <v>389</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10283,10 +10258,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10297,7 +10272,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10309,16 +10284,18 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>392</v>
+        <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10366,13 +10343,13 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
@@ -10381,13 +10358,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10395,10 +10372,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10421,13 +10398,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>158</v>
+        <v>417</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>159</v>
+        <v>418</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10478,7 +10455,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>416</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10490,13 +10467,13 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>161</v>
+        <v>419</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -10507,14 +10484,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10533,18 +10510,20 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>135</v>
+        <v>421</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>163</v>
+        <v>422</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10568,13 +10547,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10592,7 +10571,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>420</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10604,702 +10583,18 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>161</v>
+        <v>426</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN84" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:25:21+00:00</t>
+    <t>2026-10-19T13:57:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4489,10 +4489,10 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S25" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>192</v>
@@ -5511,10 +5511,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -6201,10 +6201,10 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>192</v>
@@ -7223,10 +7223,10 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>21</v>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:57:06+00:00</t>
+    <t>2026-10-19T15:00:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:00:46+00:00</t>
+    <t>2026-10-20T05:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
